--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89377</v>
+        <v>89379</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89377</v>
+        <v>89379</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89377</v>
+        <v>89379</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89379</v>
+        <v>89380</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89379</v>
+        <v>89380</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89379</v>
+        <v>89380</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89380</v>
+        <v>89386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89380</v>
+        <v>89386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89380</v>
+        <v>89386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91584</v>
+        <v>91590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89386</v>
+        <v>89390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89386</v>
+        <v>89390</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89386</v>
+        <v>89390</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91590</v>
+        <v>91594</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89390</v>
+        <v>89392</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89390</v>
+        <v>89392</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89390</v>
+        <v>89392</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
+        <v>89405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
+        <v>89405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89392</v>
+        <v>89405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91596</v>
+        <v>91609</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89405</v>
+        <v>89407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89405</v>
+        <v>89407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89405</v>
+        <v>89407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89407</v>
+        <v>89410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89407</v>
+        <v>89410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89407</v>
+        <v>89410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91611</v>
+        <v>91614</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
+        <v>89420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
+        <v>89420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
+        <v>89420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91614</v>
+        <v>91624</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89420</v>
+        <v>89421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89420</v>
+        <v>89421</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89420</v>
+        <v>89421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89421</v>
+        <v>89424</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89421</v>
+        <v>89424</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89421</v>
+        <v>89424</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91625</v>
+        <v>91628</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89424</v>
+        <v>89429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89424</v>
+        <v>89429</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89424</v>
+        <v>89429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91630</v>
+        <v>91635</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89429</v>
+        <v>89440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89429</v>
+        <v>89440</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89429</v>
+        <v>89440</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91635</v>
+        <v>91647</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89440</v>
+        <v>89441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89440</v>
+        <v>89441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89440</v>
+        <v>89441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89441</v>
+        <v>89444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89441</v>
+        <v>89444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89441</v>
+        <v>89444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91648</v>
+        <v>91651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89444</v>
+        <v>89445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108474</v>
+        <v>108476</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91659</v>
+        <v>91660</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91659</v>
+        <v>91660</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 7174-2026 artfynd.xlsx
+++ b/artfynd/A 7174-2026 artfynd.xlsx
@@ -2072,7 +2072,7 @@
         <v>136973262</v>
       </c>
       <c r="B14" t="n">
-        <v>89445</v>
+        <v>89448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>137020754</v>
       </c>
       <c r="B15" t="n">
-        <v>89444</v>
+        <v>89448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137020760</v>
       </c>
       <c r="B16" t="n">
-        <v>89444</v>
+        <v>89448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136973258</v>
       </c>
       <c r="B23" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136973278</v>
       </c>
       <c r="B24" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>136973274</v>
       </c>
       <c r="B38" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>137020758</v>
       </c>
       <c r="B40" t="n">
-        <v>91651</v>
+        <v>91655</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>136973257</v>
       </c>
       <c r="B45" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>136973256</v>
       </c>
       <c r="B53" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>136989192</v>
       </c>
       <c r="B54" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>136973261</v>
       </c>
       <c r="B73" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>136973263</v>
       </c>
       <c r="B74" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136973266</v>
       </c>
       <c r="B75" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>136973268</v>
       </c>
       <c r="B76" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>136973276</v>
       </c>
       <c r="B77" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>137020756</v>
       </c>
       <c r="B78" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137020759</v>
       </c>
       <c r="B79" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>136973270</v>
       </c>
       <c r="B83" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>136973272</v>
       </c>
       <c r="B93" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>136989189</v>
       </c>
       <c r="B94" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137020761</v>
       </c>
       <c r="B95" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>136982032</v>
       </c>
       <c r="B100" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>136973269</v>
       </c>
       <c r="B103" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>137020755</v>
       </c>
       <c r="B104" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>137020757</v>
       </c>
       <c r="B108" t="n">
-        <v>90967</v>
+        <v>90971</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>136973275</v>
       </c>
       <c r="B109" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>136973255</v>
       </c>
       <c r="B152" t="n">
-        <v>108476</v>
+        <v>108480</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>136973267</v>
       </c>
       <c r="B156" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>136989187</v>
       </c>
       <c r="B167" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>136973273</v>
       </c>
       <c r="B174" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>136989190</v>
       </c>
       <c r="B175" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>136989182</v>
       </c>
       <c r="B183" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
